--- a/output/pdf_financials_xlsx/CLC.xlsx
+++ b/output/pdf_financials_xlsx/CLC.xlsx
@@ -1936,13 +1936,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.724226</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.799215</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.506027</v>
       </c>
     </row>
     <row r="93">
@@ -3427,7 +3427,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>2.724226</v>
       </c>

--- a/output/pdf_financials_xlsx/CLC.xlsx
+++ b/output/pdf_financials_xlsx/CLC.xlsx
@@ -627,13 +627,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.013812</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.06510199999999999</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.051854</v>
       </c>
     </row>
     <row r="13">
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.131827</v>
+        <v>-4.145639</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.671814</v>
+        <v>-2.736916</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.991316</v>
+        <v>-3.04317</v>
       </c>
     </row>
     <row r="28">
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.69994</v>
+        <v>-3.713752</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.35075</v>
+        <v>-2.415852</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.650895</v>
+        <v>-2.702749</v>
       </c>
     </row>
     <row r="30">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.468028</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.761538</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.40907</v>
       </c>
     </row>
     <row r="35">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.468028</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.761538</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.40907</v>
       </c>
     </row>
     <row r="37">
@@ -1220,13 +1220,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.512117</v>
+        <v>1.044089</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.924923</v>
+        <v>0.163385</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.592563</v>
+        <v>0.183493</v>
       </c>
     </row>
     <row r="49">
@@ -2442,10 +2442,10 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.162346</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.31663</v>
       </c>
     </row>
     <row r="125">
@@ -2458,10 +2458,10 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.162346</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.31663</v>
       </c>
     </row>
     <row r="126">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4418,7 +4418,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -4848,7 +4852,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -5916,7 +5924,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
@@ -5974,7 +5982,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">

--- a/output/pdf_financials_xlsx/CLC.xlsx
+++ b/output/pdf_financials_xlsx/CLC.xlsx
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.611301</v>
       </c>
     </row>
     <row r="113">
@@ -4211,7 +4211,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CLC.xlsx
+++ b/output/pdf_financials_xlsx/CLC.xlsx
@@ -1482,13 +1482,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.5597299999999999</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.26559</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.632058</v>
       </c>
     </row>
     <row r="65">
@@ -1530,13 +1530,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>1.716641</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.886818</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.003596</v>
       </c>
     </row>
     <row r="68">
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.191208</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.680765</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.320682</v>
       </c>
     </row>
     <row r="111">
@@ -3716,7 +3716,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>0.191208</v>
       </c>
